--- a/modulo-04-isr-personas-fisicas/clase-01-regimenes-fiscales-pf/ejercicios-excel/02-resico-vs-612.xlsx
+++ b/modulo-04-isr-personas-fisicas/clase-01-regimenes-fiscales-pf/ejercicios-excel/02-resico-vs-612.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ejercicio" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Solución" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejercicio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solución" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,7 +916,7 @@
         <v>667687.0699999999</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2009098.96</v>
+        <v>1276925.98</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>125215.26</v>
@@ -930,13 +930,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="8" t="n">
-        <v>2009098.97</v>
+        <v>1276925.99</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2678798.66</v>
+        <v>1702567.97</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>527638.8199999999</v>
+        <v>307989.62</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>0.32</v>
@@ -947,13 +947,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="n">
-        <v>2678798.67</v>
+        <v>1702567.98</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8036395.93</v>
+        <v>5107703.9</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>741942.8199999999</v>
+        <v>448131.88</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>0.34</v>
@@ -964,13 +964,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="n">
-        <v>8036395.94</v>
+        <v>5107703.91</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>999999999.99</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>2563435.86</v>
+        <v>1606771.1</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>0.35</v>
